--- a/학교 연수 전자서명 시스템 - 배포용 원본.xlsx
+++ b/학교 연수 전자서명 시스템 - 배포용 원본.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 사용설명서" sheetId="1" r:id="R250fbade093b48b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 사용설명서" sheetId="1" r:id="R452e5c6d523b43c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="10">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -69,8 +69,25 @@
       <x:color rgb="FF64748B"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF17233B"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF34425E"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="16">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -147,8 +164,23 @@
         <x:fgColor rgb="FFE9EEF5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2463EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF3FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="34">
+  <x:borders count="35">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -460,13 +492,27 @@
       </x:top>
       <x:bottom style="thin">
         <x:color rgb="FFB42318"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC9D6F0"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFC9D6F0"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC9D6F0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFC9D6F0"/>
       </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="124">
+  <x:cellXfs count="136">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -831,6 +877,42 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="16" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="16" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="17" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="17" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1486,11 +1568,11 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C32" s="66" t="str">
-        <x:v>출력 미리보기</x:v>
+        <x:v>미서명 현황 확인</x:v>
       </x:c>
       <x:c r="D32" s="32" t="str">
-        <x:v>연수 목록의 출력 버튼에서 날짜·열 수·정렬·서명률·PDF/엑셀/인쇄를 고릅니다.
-참고  실제 서명 이미지가 들어간 A4 미리보기를 먼저 확인합니다.</x:v>
+        <x:v>연수 목록의 미서명 현황에서 해당 날짜의 미서명자를 확인합니다.
+참고  전체 현황으로 전환하면 서명 여부·완료 시각·서명률을 함께 볼 수 있습니다.</x:v>
       </x:c>
       <x:c r="E32" s="109"/>
       <x:c r="F32" s="3"/>
@@ -1501,11 +1583,11 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C33" s="66" t="str">
-        <x:v>파일 보관</x:v>
+        <x:v>출력 미리보기</x:v>
       </x:c>
       <x:c r="D33" s="32" t="str">
-        <x:v>PDF 또는 엑셀을 내려받아 학교가 정한 보관 위치에 저장합니다.
-참고  인쇄하기만 실행한 작업은 원본 삭제 조건을 충족하지 않습니다.</x:v>
+        <x:v>연수 목록의 출력 버튼에서 날짜·열 수·정렬·서명률·PDF·엑셀·인쇄를 고릅니다.
+참고  실제 서명 이미지가 들어간 A4 미리보기를 먼저 확인하며 단계별 진행 상태가 표시됩니다.</x:v>
       </x:c>
       <x:c r="E33" s="109"/>
       <x:c r="F33" s="3"/>
@@ -1516,20 +1598,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C34" s="66" t="str">
+        <x:v>파일 보관</x:v>
+      </x:c>
+      <x:c r="D34" s="32" t="str">
+        <x:v>PDF 또는 엑셀을 내려받아 학교가 정한 보관 위치에 저장합니다.
+참고  인쇄하기만 실행한 작업은 원본 삭제 조건을 충족하지 않습니다.</x:v>
+      </x:c>
+      <x:c r="E34" s="109"/>
+      <x:c r="F34" s="3"/>
+    </x:row>
+    <x:row r="35" ht="43.5" customHeight="1">
+      <x:c r="A35" s="3"/>
+      <x:c r="B35" s="127" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C35" s="131" t="str">
         <x:v>원본 삭제</x:v>
       </x:c>
-      <x:c r="D34" s="32" t="str">
+      <x:c r="D35" s="135" t="str">
         <x:v>보관 파일을 확인한 뒤 연수명을 다시 입력해 해당 날짜의 원본 서명과 PNG를 삭제합니다.
 참고  출력 파일은 비공개 Drive의 출력 보관 폴더에 남습니다.</x:v>
       </x:c>
-      <x:c r="E34" s="109"/>
-      <x:c r="F34" s="3"/>
-    </x:row>
-    <x:row r="35" ht="20.25" customHeight="1">
-      <x:c r="A35" s="3"/>
-      <x:c r="B35" s="104"/>
-      <x:c r="C35" s="3"/>
-      <x:c r="D35" s="3"/>
       <x:c r="E35" s="105"/>
       <x:c r="F35" s="3"/>
     </x:row>

--- a/학교 연수 전자서명 시스템 - 배포용 원본.xlsx
+++ b/학교 연수 전자서명 시스템 - 배포용 원본.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 사용설명서" sheetId="1" r:id="R7f308dd26ef541a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📘 사용설명서" sheetId="1" r:id="R22398b158c734fa3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1478,7 +1478,7 @@
       <x:c r="E25" s="109"/>
       <x:c r="F25" s="3"/>
     </x:row>
-    <x:row r="26" ht="43.5" customHeight="1">
+    <x:row r="26" ht="42" customHeight="1">
       <x:c r="A26" s="3"/>
       <x:c r="B26" s="115" t="str">
         <x:v>4</x:v>
@@ -1487,8 +1487,8 @@
         <x:v>연수 등록</x:v>
       </x:c>
       <x:c r="D26" s="32" t="str">
-        <x:v>연수에서 새 연수를 만들고 날짜·시간·활성 상태를 정합니다.
-참고  특정 날짜 또는 매일 진행 방식을 선택할 수 있습니다.</x:v>
+        <x:v>연수에서 날짜·시간·활성 상태와 서명 대상(전체 구성원 또는 부서 선택)을 정합니다.
+참고  선택한 부서에 나중에 추가되는 구성원도 자동으로 대상에 포함됩니다. 지난 연수도 활성화하면 재수합할 수 있습니다.</x:v>
       </x:c>
       <x:c r="E26" s="109"/>
       <x:c r="F26" s="3"/>
